--- a/papers_excluded_after_fulltext_screening.xlsx
+++ b/papers_excluded_after_fulltext_screening.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\drive_gmail\Recherche\Article 34 - EBI-ADHD\data_analysis\supplementary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\drive_gmail\Recherche\Article 34 - EBI-ADHD\data_analysis\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE84DF5A-2F8A-48BA-80EF-D3DA7959AB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6C4655-236C-4889-B064-BB76D77E6981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$D$300</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1058,11 +1057,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1113,11 +1119,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1338,7 +1345,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="75.36328125" customWidth="1"/>
+    <col min="2" max="2" width="113.90625" customWidth="1"/>
     <col min="3" max="3" width="50.54296875" customWidth="1"/>
     <col min="4" max="26" width="10.81640625" customWidth="1"/>
   </cols>
@@ -2187,7 +2194,7 @@
         <v>96</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2253,7 +2260,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -4185,7 +4192,7 @@
       <c r="A259" s="1">
         <v>568</v>
       </c>
-      <c r="B259" s="2" t="s">
+      <c r="B259" s="5" t="s">
         <v>287</v>
       </c>
       <c r="C259" t="s">
@@ -4201,7 +4208,7 @@
         <v>288</v>
       </c>
       <c r="C260" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
